--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487701_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487701_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9751</v>
+        <v>3.0634</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8981</v>
+        <v>3.259</v>
       </c>
       <c r="F2" t="n">
-        <v>0.077</v>
+        <v>-0.1956</v>
       </c>
       <c r="G2" t="n">
         <v>4.6625</v>
@@ -610,13 +610,13 @@
         <v>2.7164</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4621</v>
+        <v>-0.3737</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9085</v>
+        <v>-0.5476</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4464</v>
+        <v>0.1739</v>
       </c>
       <c r="V2" t="n">
         <v>-2.7776</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1938</v>
+        <v>1.87</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6664</v>
+        <v>-0.4451</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8602</v>
+        <v>2.3151</v>
       </c>
       <c r="G3" t="n">
         <v>0.771</v>
@@ -688,13 +688,13 @@
         <v>2.1344</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6169</v>
+        <v>0.293</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5204</v>
+        <v>-0.2992</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1373</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0.6119</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6158</v>
+        <v>1.3732</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9357</v>
+        <v>0.8566</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6801</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>1.4713</v>
@@ -766,13 +766,13 @@
         <v>0.9702</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4966</v>
+        <v>0.254</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2075</v>
+        <v>0.1284</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2892</v>
+        <v>0.1256</v>
       </c>
       <c r="V4" t="n">
         <v>-1.1283</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. HERMOSO ALCUBILLA</t>
+          <t>J. MARTINEZ SANTOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8603</v>
+        <v>0.849</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4296</v>
+        <v>0.2711</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2899</v>
+        <v>0.5779</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5454</v>
+        <v>0.5974</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6988</v>
+        <v>0.1854</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1534</v>
+        <v>0.4121</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7815</v>
+        <v>1.444</v>
       </c>
       <c r="K5" t="n">
-        <v>2.035</v>
+        <v>0.7538</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2535</v>
+        <v>0.6901</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2361</v>
+        <v>-0.8466</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3362</v>
+        <v>-0.5685</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1</v>
+        <v>-0.2781</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5821</v>
+        <v>0.5821</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3284</v>
+        <v>1.5523</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2851</v>
+        <v>-0.3306</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4755</v>
+        <v>-0.2027</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1904</v>
+        <v>-0.1278</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6081</v>
+        <v>0.6899</v>
       </c>
       <c r="E6" t="n">
         <v>-0.411</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0191</v>
+        <v>1.1009</v>
       </c>
       <c r="G6" t="n">
         <v>0.7353</v>
@@ -922,13 +922,13 @@
         <v>0.9702</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1272</v>
+        <v>-0.0454</v>
       </c>
       <c r="T6" t="n">
         <v>-0.1817</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0545</v>
+        <v>0.1363</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANTOS</t>
+          <t>M. HERMOSO ALCUBILLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5248</v>
+        <v>0.2079</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1104</v>
+        <v>-1.1093</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4143</v>
+        <v>1.3172</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5974</v>
+        <v>0.5454</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1854</v>
+        <v>1.6988</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4121</v>
+        <v>-1.1534</v>
       </c>
       <c r="J7" t="n">
-        <v>1.444</v>
+        <v>0.7815</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7538</v>
+        <v>2.035</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6901</v>
+        <v>-1.2535</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8466</v>
+        <v>-0.2361</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5685</v>
+        <v>-0.3362</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2781</v>
+        <v>0.1</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5821</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5523</v>
+        <v>2.3284</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6548</v>
+        <v>-0.3673</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3634</v>
+        <v>-0.2042</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2914</v>
+        <v>-0.1631</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. PASCUAL COZAR</t>
+          <t>N. LASUNCION MARIBLANCA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8324</v>
+        <v>-0.3693</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6234</v>
+        <v>-0.3819</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7911</v>
+        <v>0.0126</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2717</v>
+        <v>0.3583</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3378</v>
+        <v>-0.2389</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6095</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6782</v>
+        <v>0.0208</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3099</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6318</v>
+        <v>0.614</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9499</v>
+        <v>0.3375</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9721</v>
+        <v>0.3542</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0223</v>
+        <v>-0.0167</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3881</v>
+        <v>0.3881</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9403</v>
+        <v>-1.1642</v>
       </c>
       <c r="R8" t="n">
         <v>1.5523</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3279</v>
+        <v>-1.1157</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6169</v>
+        <v>-0.4624</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.711</v>
+        <v>-0.6533</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6119</v>
+        <v>1.2239</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. LASUNCION MARIBLANCA</t>
+          <t>E. PASCUAL COZAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8604000000000001</v>
+        <v>-0.4353</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6822</v>
+        <v>-2.3627</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1782</v>
+        <v>1.9273</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3583</v>
+        <v>0.2717</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2389</v>
+        <v>-0.3378</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6095</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0208</v>
+        <v>-0.6782</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-1.3099</v>
       </c>
       <c r="L9" t="n">
-        <v>0.614</v>
+        <v>0.6318</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3375</v>
+        <v>0.9499</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3542</v>
+        <v>0.9721</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0167</v>
+        <v>-0.0223</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3881</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1642</v>
+        <v>-1.9403</v>
       </c>
       <c r="R9" t="n">
         <v>1.5523</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6068</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7627</v>
+        <v>-0.3561</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8441</v>
+        <v>-0.5748</v>
       </c>
       <c r="V9" t="n">
+        <v>0.6119</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.6119</v>
+      </c>
+      <c r="X9" t="n">
         <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.2239</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-1.2239</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3182</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6378</v>
+        <v>-2.3771</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3197</v>
+        <v>1.6195</v>
       </c>
       <c r="G10" t="n">
         <v>1.8467</v>
@@ -1234,13 +1234,13 @@
         <v>2.3284</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0126</v>
+        <v>-0.452</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8962</v>
+        <v>-0.6354</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1164</v>
+        <v>0.1834</v>
       </c>
       <c r="V10" t="n">
         <v>0.5642</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8147</v>
+        <v>-2.1968</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9665</v>
+        <v>-2.2668</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1518</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7336</v>
@@ -1312,13 +1312,13 @@
         <v>1.7463</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5155</v>
+        <v>-0.8975</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1559</v>
+        <v>-0.4562</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3595</v>
+        <v>-0.4413</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1179</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4776</v>
+        <v>-2.214</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2489</v>
+        <v>-2.1488</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2287</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>0.2964</v>
@@ -1390,13 +1390,13 @@
         <v>0.5821</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7277</v>
+        <v>-0.464</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0236</v>
+        <v>0.0765</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-0.5406</v>
       </c>
       <c r="V12" t="n">
         <v>0.2821</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4746</v>
+        <v>2.080400000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.7216</v>
+        <v>-7.116</v>
       </c>
       <c r="F13" t="n">
         <v>9.196299999999999</v>
@@ -1459,7 +1459,7 @@
         <v>-0.195</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9700999999999997</v>
+        <v>-0.9701000000000002</v>
       </c>
       <c r="Q13" t="n">
         <v>-19.4032</v>
@@ -1468,28 +1468,28 @@
         <v>18.4333</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.036</v>
+        <v>-4.4301</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.7463</v>
+        <v>-3.140600000000001</v>
       </c>
       <c r="U13" t="n">
         <v>-1.2895</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.3418</v>
+        <v>-3.341800000000001</v>
       </c>
       <c r="W13" t="n">
         <v>5.6462</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.987900000000002</v>
+        <v>-8.9879</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. SCHUCH</t>
+          <t>M. ESTAPE ROIZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3949</v>
+        <v>5.4719</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4912</v>
+        <v>1.6047</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9036</v>
+        <v>3.8672</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2195</v>
+        <v>2.9623</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3157</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9036999999999999</v>
+        <v>2.0354</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8393</v>
+        <v>2.2303</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3192</v>
+        <v>0.9845</v>
       </c>
       <c r="L14" t="n">
-        <v>0.52</v>
+        <v>1.2458</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6198</v>
+        <v>0.732</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0035</v>
+        <v>-0.0577</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3837</v>
+        <v>0.7897</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5523</v>
+        <v>1.7463</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5224</v>
+        <v>2.7164</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9888</v>
+        <v>1.1678</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2719</v>
+        <v>0.3446</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2831</v>
+        <v>0.8233</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6119</v>
+        <v>-0.4045</v>
       </c>
       <c r="W14" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2821</v>
+        <v>-0.4045</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. ESTAPE ROIZ</t>
+          <t>B. SCHUCH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2007</v>
+        <v>4.5477</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3034</v>
+        <v>2.1919</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8973</v>
+        <v>2.3557</v>
       </c>
       <c r="G15" t="n">
-        <v>2.9623</v>
+        <v>2.2195</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9268999999999999</v>
+        <v>1.3157</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0354</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2303</v>
+        <v>2.8393</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9845</v>
+        <v>2.3192</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2458</v>
+        <v>0.52</v>
       </c>
       <c r="M15" t="n">
-        <v>0.732</v>
+        <v>-0.6198</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0577</v>
+        <v>-1.0035</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7897</v>
+        <v>0.3837</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7463</v>
+        <v>1.5523</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7164</v>
+        <v>2.5224</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1034</v>
+        <v>0.164</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9567</v>
+        <v>-0.5712</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1467</v>
+        <v>0.7352</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.4045</v>
+        <v>0.6119</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4045</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. GOMA</t>
+          <t>S. COULIBALY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4998</v>
+        <v>1.7472</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4177</v>
+        <v>0.4713</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0821</v>
+        <v>1.276</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.4715</v>
+        <v>-1.3049</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.2057</v>
+        <v>-0.3773</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2659</v>
+        <v>-0.9276</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.7613</v>
+        <v>-0.2413</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.9237</v>
+        <v>-0.4037</v>
       </c>
       <c r="L16" t="n">
         <v>0.1624</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7102</v>
+        <v>-1.0637</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.282</v>
+        <v>0.0263</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4282</v>
+        <v>-1.09</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3881</v>
+        <v>0.194</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5224</v>
+        <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>3.9594</v>
+        <v>0.7402</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1253</v>
+        <v>0.535</v>
       </c>
       <c r="U16" t="n">
-        <v>1.8341</v>
+        <v>0.2053</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4</v>
+        <v>2.1179</v>
       </c>
       <c r="W16" t="n">
-        <v>2.9641</v>
+        <v>2.1179</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. COULIBALY</t>
+          <t>G. GOMA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1476</v>
+        <v>0.7084</v>
       </c>
       <c r="E17" t="n">
-        <v>1.272</v>
+        <v>-0.9837</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8756</v>
+        <v>1.6921</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3049</v>
+        <v>-3.4715</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3773</v>
+        <v>-3.2057</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9276</v>
+        <v>-0.2659</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2413</v>
+        <v>-1.7613</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4037</v>
+        <v>-1.9237</v>
       </c>
       <c r="L17" t="n">
         <v>0.1624</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0637</v>
+        <v>-1.7102</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0263</v>
+        <v>-1.282</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.09</v>
+        <v>-0.4282</v>
       </c>
       <c r="P17" t="n">
-        <v>0.194</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1344</v>
+        <v>2.5224</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1406</v>
+        <v>2.168</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3358</v>
+        <v>0.7239</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1951</v>
+        <v>1.4441</v>
       </c>
       <c r="V17" t="n">
-        <v>2.1179</v>
+        <v>2.4</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1179</v>
+        <v>2.9641</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0712</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0365</v>
+        <v>-0.2647</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0346</v>
+        <v>0.1981</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7637</v>
@@ -1858,13 +1858,13 @@
         <v>1.1642</v>
       </c>
       <c r="S18" t="n">
-        <v>2.6572</v>
+        <v>1.5194</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3183</v>
+        <v>1.017</v>
       </c>
       <c r="U18" t="n">
-        <v>0.339</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0164</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1058</v>
+        <v>-0.6063</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2425</v>
+        <v>-0.258</v>
       </c>
       <c r="F19" t="n">
         <v>-0.3483</v>
@@ -1936,10 +1936,10 @@
         <v>1.7463</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8737</v>
+        <v>0.3732</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6079</v>
+        <v>0.1074</v>
       </c>
       <c r="U19" t="n">
         <v>0.2658</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1391</v>
+        <v>-1.8111</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8557</v>
+        <v>-2.2551</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7166</v>
+        <v>0.444</v>
       </c>
       <c r="G20" t="n">
         <v>-2.5136</v>
@@ -2014,13 +2014,13 @@
         <v>1.1642</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3028</v>
+        <v>0.6309</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7145</v>
+        <v>-0.1139</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0173</v>
+        <v>0.7447</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1224</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6844</v>
+        <v>-1.8169</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.6958</v>
+        <v>-3.0952</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0114</v>
+        <v>1.2783</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9378</v>
@@ -2092,13 +2092,13 @@
         <v>1.9403</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4004</v>
+        <v>0.4671</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8962</v>
+        <v>-0.2956</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4958</v>
+        <v>0.7627</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3463</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2011</v>
+        <v>-2.5765</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9029</v>
+        <v>-3.6026</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7018</v>
+        <v>1.0261</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4957</v>
@@ -2170,13 +2170,13 @@
         <v>1.7463</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2977</v>
+        <v>0.9222</v>
       </c>
       <c r="T22" t="n">
-        <v>0.074</v>
+        <v>0.3743</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2237</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>1.1015</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6584</v>
+        <v>-4.4032</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5052</v>
+        <v>-3.0047</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1532</v>
+        <v>-1.3985</v>
       </c>
       <c r="G23" t="n">
         <v>-4.1196</v>
@@ -2248,13 +2248,13 @@
         <v>1.7463</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.703</v>
+        <v>-0.4478</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3325</v>
+        <v>-0.832</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3706</v>
+        <v>0.3842</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6119</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.474600000000002</v>
+        <v>1.194600000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.196300000000001</v>
+        <v>-9.196100000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>7.721500000000001</v>
+        <v>10.3907</v>
       </c>
       <c r="G24" t="n">
         <v>-10.8224</v>
@@ -2326,13 +2326,13 @@
         <v>19.40320000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>5.035799999999999</v>
+        <v>7.705000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>1.289499999999999</v>
+        <v>1.2895</v>
       </c>
       <c r="U24" t="n">
-        <v>3.7464</v>
+        <v>6.4157</v>
       </c>
       <c r="V24" t="n">
         <v>3.3417</v>
